--- a/data/trans_orig/P5701-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5701-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2007</t>
+          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>234301</t>
+          <t>236447</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>285527</t>
+          <t>287924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222049</t>
+          <t>217255</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>271631</t>
+          <t>270996</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>469875</t>
+          <t>470456</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>542154</t>
+          <t>541439</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194891</t>
+          <t>195543</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>241645</t>
+          <t>242606</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>195725</t>
+          <t>196198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242120</t>
+          <t>245866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>400433</t>
+          <t>402656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>471788</t>
+          <t>471928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>159431</t>
+          <t>159925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>204453</t>
+          <t>207235</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>142913</t>
+          <t>142959</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>187652</t>
+          <t>186367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>312969</t>
+          <t>312807</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>379546</t>
+          <t>376505</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>20354</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44493</t>
+          <t>42594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40162</t>
+          <t>40570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70442</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67664</t>
+          <t>67403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104575</t>
+          <t>105304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>410422</t>
+          <t>411365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>475235</t>
+          <t>473366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>358529</t>
+          <t>363268</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>425101</t>
+          <t>422752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>789735</t>
+          <t>791864</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>876490</t>
+          <t>882417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243858</t>
+          <t>242871</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300327</t>
+          <t>299457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267025</t>
+          <t>264896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323422</t>
+          <t>326076</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>524294</t>
+          <t>529408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>609470</t>
+          <t>607783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>167406</t>
+          <t>166588</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>218342</t>
+          <t>219153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>175186</t>
+          <t>176222</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>231110</t>
+          <t>229091</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>361835</t>
+          <t>358612</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>433211</t>
+          <t>430065</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55387</t>
+          <t>52760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50946</t>
+          <t>51900</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83521</t>
+          <t>85930</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88335</t>
+          <t>87346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130054</t>
+          <t>128726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27240</t>
+          <t>29490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24648</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>44388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>329507</t>
+          <t>329813</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382836</t>
+          <t>382092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>288366</t>
+          <t>290885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>338557</t>
+          <t>340858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>633302</t>
+          <t>636916</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>706357</t>
+          <t>706768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147310</t>
+          <t>148094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193441</t>
+          <t>193482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159788</t>
+          <t>163744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205249</t>
+          <t>208702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>319032</t>
+          <t>323203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>382406</t>
+          <t>387456</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84153</t>
+          <t>85524</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>122669</t>
+          <t>122363</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92969</t>
+          <t>93109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>130860</t>
+          <t>131824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>186915</t>
+          <t>188156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>238694</t>
+          <t>241769</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>23633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49171</t>
+          <t>50886</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44489</t>
+          <t>45210</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73893</t>
+          <t>73924</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76621</t>
+          <t>77325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113546</t>
+          <t>113757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24894</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27916</t>
+          <t>29337</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47980</t>
+          <t>46356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>383749</t>
+          <t>384053</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>442159</t>
+          <t>444214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>424533</t>
+          <t>426213</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>489697</t>
+          <t>490371</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>830411</t>
+          <t>827969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>919034</t>
+          <t>920447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>227562</t>
+          <t>227847</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>281252</t>
+          <t>279590</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240193</t>
+          <t>240889</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>297118</t>
+          <t>293756</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>483678</t>
+          <t>483071</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>559541</t>
+          <t>560315</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162960</t>
+          <t>161323</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>209567</t>
+          <t>211710</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>152858</t>
+          <t>151703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>201286</t>
+          <t>200688</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>329181</t>
+          <t>328521</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>399751</t>
+          <t>394926</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56467</t>
+          <t>57513</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90755</t>
+          <t>94382</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90115</t>
+          <t>90721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131245</t>
+          <t>131369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158577</t>
+          <t>158566</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>208668</t>
+          <t>209875</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30656</t>
+          <t>29550</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40361</t>
+          <t>38926</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31519</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61059</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1423836</t>
+          <t>1417007</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1536681</t>
+          <t>1529384</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1355072</t>
+          <t>1360209</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1468240</t>
+          <t>1469151</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2796749</t>
+          <t>2806532</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2958658</t>
+          <t>2964400</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>854500</t>
+          <t>863741</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>960230</t>
+          <t>966032</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,82 +3589,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>964005</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>916465</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1018528</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>27,12%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1874147</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1803166</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1951025</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>28,16%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>29,31%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>964005</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>914117</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1020487</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>28,53%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>30,2%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1874147</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1800298</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1953065</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>619831</t>
+          <t>618861</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>707230</t>
+          <t>707187</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>604703</t>
+          <t>605616</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>696795</t>
+          <t>694996</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1248415</t>
+          <t>1246598</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1383194</t>
+          <t>1378754</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>154388</t>
+          <t>153540</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>207066</t>
+          <t>207773</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>258626</t>
+          <t>258619</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>323117</t>
+          <t>323875</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>425355</t>
+          <t>423859</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>516570</t>
+          <t>507131</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>71163</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>46213</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>81212</t>
+          <t>81273</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>91593</t>
+          <t>92518</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>139295</t>
+          <t>140720</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2012</t>
+          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>393735</t>
+          <t>396023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>448866</t>
+          <t>450324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>361577</t>
+          <t>362034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>413562</t>
+          <t>415624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>767810</t>
+          <t>772711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>846949</t>
+          <t>847324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132993</t>
+          <t>135036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179189</t>
+          <t>178030</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149900</t>
+          <t>149133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194824</t>
+          <t>196596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>296381</t>
+          <t>292655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>357694</t>
+          <t>361898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77052</t>
+          <t>77829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116493</t>
+          <t>115525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62282</t>
+          <t>63133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96729</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>148893</t>
+          <t>147378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>201683</t>
+          <t>198700</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14143</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33381</t>
+          <t>33520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36841</t>
+          <t>38044</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67413</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57614</t>
+          <t>58210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94992</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15111</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25054</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>533062</t>
+          <t>539875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>601639</t>
+          <t>604143</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>528973</t>
+          <t>527695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>594214</t>
+          <t>593483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,47 +5107,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>57,5%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1129701</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1086092</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1177173</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>55,24%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>53,11%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>57,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1129701</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1083088</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1176323</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>55,24%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>52,96%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>211209</t>
+          <t>212984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>269130</t>
+          <t>265715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244766</t>
+          <t>245597</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>300960</t>
+          <t>305409</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>472046</t>
+          <t>473288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>552121</t>
+          <t>555596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120437</t>
+          <t>121029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166027</t>
+          <t>165691</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119222</t>
+          <t>118488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164164</t>
+          <t>162179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>250761</t>
+          <t>252704</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>314010</t>
+          <t>316381</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>42173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74591</t>
+          <t>77053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31130</t>
+          <t>31726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57809</t>
+          <t>56724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79365</t>
+          <t>79701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122628</t>
+          <t>123089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26668</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34229</t>
+          <t>34330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>383166</t>
+          <t>384025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>440902</t>
+          <t>442855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>377479</t>
+          <t>379797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>435351</t>
+          <t>436142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>782537</t>
+          <t>780874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>864526</t>
+          <t>863231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148720</t>
+          <t>148887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199108</t>
+          <t>197934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158642</t>
+          <t>157501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206813</t>
+          <t>207421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>322425</t>
+          <t>325435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>390900</t>
+          <t>392220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90911</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130451</t>
+          <t>130650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93131</t>
+          <t>92128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>135857</t>
+          <t>132102</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>195854</t>
+          <t>193279</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>253920</t>
+          <t>252512</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62542</t>
+          <t>62603</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45505</t>
+          <t>46955</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78338</t>
+          <t>78291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88730</t>
+          <t>86679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132010</t>
+          <t>130240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21143</t>
+          <t>22224</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40349</t>
+          <t>39584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>451386</t>
+          <t>452426</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>512612</t>
+          <t>514000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>481312</t>
+          <t>483125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>546453</t>
+          <t>548217</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>952303</t>
+          <t>947200</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1036656</t>
+          <t>1039220</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237044</t>
+          <t>232073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291779</t>
+          <t>289923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>270769</t>
+          <t>271801</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331671</t>
+          <t>329987</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>523875</t>
+          <t>522325</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>601678</t>
+          <t>605471</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>126706</t>
+          <t>127061</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>175528</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>122114</t>
+          <t>125472</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>168720</t>
+          <t>167862</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>262039</t>
+          <t>261794</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>327735</t>
+          <t>327015</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31569</t>
+          <t>32511</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58231</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59864</t>
+          <t>58427</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94129</t>
+          <t>93447</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96670</t>
+          <t>99032</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138658</t>
+          <t>143784</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>37599</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1826436</t>
+          <t>1827244</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1940798</t>
+          <t>1945721</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1805516</t>
+          <t>1808176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1927639</t>
+          <t>1933041</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3676481</t>
+          <t>3668352</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3848042</t>
+          <t>3836888</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>771021</t>
+          <t>775622</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>878971</t>
+          <t>875762</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>870554</t>
+          <t>878893</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>982018</t>
+          <t>988170</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1678560</t>
+          <t>1675369</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1831549</t>
+          <t>1827362</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>456324</t>
+          <t>454854</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>545708</t>
+          <t>542023</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>436010</t>
+          <t>439595</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>518080</t>
+          <t>518142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>909826</t>
+          <t>912929</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1032793</t>
+          <t>1035570</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>142938</t>
+          <t>142875</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>199131</t>
+          <t>197493</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>201592</t>
+          <t>203350</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>259851</t>
+          <t>265118</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>360495</t>
+          <t>358975</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>440400</t>
+          <t>444082</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26215</t>
+          <t>26345</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>54108</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>68515</t>
+          <t>68331</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70266</t>
+          <t>70809</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>109501</t>
+          <t>111622</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2016</t>
+          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>274797</t>
+          <t>275847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>327612</t>
+          <t>327812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>242186</t>
+          <t>243728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291321</t>
+          <t>298323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>534251</t>
+          <t>531935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>604527</t>
+          <t>602365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214315</t>
+          <t>215314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265603</t>
+          <t>263690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235562</t>
+          <t>231905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285733</t>
+          <t>284811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465935</t>
+          <t>463787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>536255</t>
+          <t>531045</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84266</t>
+          <t>82487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>119735</t>
+          <t>120262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81785</t>
+          <t>81774</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120616</t>
+          <t>119306</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>175065</t>
+          <t>176735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>227216</t>
+          <t>229257</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40483</t>
+          <t>41383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25957</t>
+          <t>25807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50801</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49123</t>
+          <t>49843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82393</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>415826</t>
+          <t>418646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>482124</t>
+          <t>484980</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>369642</t>
+          <t>372874</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>434725</t>
+          <t>432631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>808022</t>
+          <t>805803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>901820</t>
+          <t>897425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>356838</t>
+          <t>358364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421486</t>
+          <t>421294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>409029</t>
+          <t>408863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>470107</t>
+          <t>470528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>782883</t>
+          <t>781540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>875515</t>
+          <t>872355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110981</t>
+          <t>111812</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156706</t>
+          <t>155153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118714</t>
+          <t>117080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162807</t>
+          <t>163476</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>239098</t>
+          <t>242420</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>303805</t>
+          <t>307336</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>36807</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66851</t>
+          <t>64108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37726</t>
+          <t>36698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67169</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80213</t>
+          <t>79515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122302</t>
+          <t>119955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20708</t>
+          <t>21856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>23113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>282185</t>
+          <t>284291</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>336683</t>
+          <t>340426</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290956</t>
+          <t>289184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>345809</t>
+          <t>344760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>585362</t>
+          <t>592968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>666035</t>
+          <t>670755</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>252938</t>
+          <t>251556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>306878</t>
+          <t>308173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>259326</t>
+          <t>257766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>311537</t>
+          <t>311769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>528634</t>
+          <t>524147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>605451</t>
+          <t>603737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106538</t>
+          <t>104683</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>149950</t>
+          <t>148399</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>123041</t>
+          <t>122165</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>168741</t>
+          <t>168531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>239187</t>
+          <t>241033</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>302741</t>
+          <t>299693</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22905</t>
+          <t>22784</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48034</t>
+          <t>46713</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45493</t>
+          <t>45823</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50640</t>
+          <t>52487</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84516</t>
+          <t>86082</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21977</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>359193</t>
+          <t>359331</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>421653</t>
+          <t>420403</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>408335</t>
+          <t>413621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>476708</t>
+          <t>474290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>788197</t>
+          <t>788915</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>880507</t>
+          <t>877348</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>310885</t>
+          <t>311681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>371428</t>
+          <t>371217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>354771</t>
+          <t>350885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>417987</t>
+          <t>413273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>679029</t>
+          <t>681057</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>769003</t>
+          <t>765926</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>128880</t>
+          <t>130264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>176697</t>
+          <t>176059</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125703</t>
+          <t>125609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>173074</t>
+          <t>171571</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>267435</t>
+          <t>269003</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>336526</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54377</t>
+          <t>55083</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45517</t>
+          <t>47021</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77320</t>
+          <t>78939</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>84661</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121776</t>
+          <t>127453</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>16084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31446</t>
+          <t>31926</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1389426</t>
+          <t>1390324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1507118</t>
+          <t>1509621</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1376176</t>
+          <t>1375855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1492439</t>
+          <t>1492138</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2804996</t>
+          <t>2800998</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2964954</t>
+          <t>2969043</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1194361</t>
+          <t>1192874</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1313291</t>
+          <t>1306138</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1308943</t>
+          <t>1308061</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1422741</t>
+          <t>1424247</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2528213</t>
+          <t>2528869</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2689286</t>
+          <t>2695303</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>469007</t>
+          <t>473096</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>556226</t>
+          <t>557011</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>486655</t>
+          <t>489368</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>573450</t>
+          <t>576524</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>984702</t>
+          <t>982970</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1102066</t>
+          <t>1101053</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>127106</t>
+          <t>127900</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>179378</t>
+          <t>178899</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>155158</t>
+          <t>156679</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>212450</t>
+          <t>210596</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>294900</t>
+          <t>295481</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>370728</t>
+          <t>368828</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38209</t>
+          <t>39439</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>19849</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44641</t>
+          <t>42929</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>42321</t>
+          <t>43161</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>76906</t>
+          <t>75032</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2023</t>
+          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>319991</t>
+          <t>313626</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>373901</t>
+          <t>372272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,82 +11674,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>49,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>351060</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>331650</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>373049</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>52,06%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>49,18%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>55,32%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>695940</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>659994</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>732158</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>53,17%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>50,42%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>351060</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>329254</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>371536</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,06%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>48,83%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>55,1%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>695940</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>662424</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>731977</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>53,17%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>50,61%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162568</t>
+          <t>164466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>211360</t>
+          <t>214766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,17 +11802,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>223152</t>
+          <t>223151</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205450</t>
+          <t>203745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242949</t>
+          <t>241939</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>380140</t>
+          <t>379572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442040</t>
+          <t>441987</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48050</t>
+          <t>47274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77775</t>
+          <t>75511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44726</t>
+          <t>45077</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65322</t>
+          <t>65708</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98165</t>
+          <t>97179</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133796</t>
+          <t>134183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21199</t>
+          <t>21402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42516</t>
+          <t>43392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>28246</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46340</t>
+          <t>46971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54805</t>
+          <t>55783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83597</t>
+          <t>83448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23704</t>
+          <t>22475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32173</t>
+          <t>33867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>674340</t>
+          <t>674339</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>674340</t>
+          <t>674339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>674340</t>
+          <t>674339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>619293</t>
+          <t>614319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>953719</t>
+          <t>988986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>431936</t>
+          <t>432538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>487257</t>
+          <t>485270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1072319</t>
+          <t>1068797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1516583</t>
+          <t>1525432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169592</t>
+          <t>158625</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421328</t>
+          <t>422093</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>317720</t>
+          <t>318456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>369251</t>
+          <t>366740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>446233</t>
+          <t>443685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>763451</t>
+          <t>767211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36557</t>
+          <t>37142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106393</t>
+          <t>109719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66879</t>
+          <t>68827</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93807</t>
+          <t>96859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105330</t>
+          <t>99456</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>188860</t>
+          <t>186173</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>54382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>46429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72157</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64930</t>
+          <t>62627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115901</t>
+          <t>116870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42517</t>
+          <t>43720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>344180</t>
+          <t>346090</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>405196</t>
+          <t>408978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196663</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>483721</t>
+          <t>486881</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>485029</t>
+          <t>495012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>862661</t>
+          <t>868614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213611</t>
+          <t>210290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271144</t>
+          <t>269931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140199</t>
+          <t>121907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>331934</t>
+          <t>328627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332720</t>
+          <t>332489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569006</t>
+          <t>571339</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40366</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75360</t>
+          <t>76935</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85130</t>
+          <t>86734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>561889</t>
+          <t>595548</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>137915</t>
+          <t>137149</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>750269</t>
+          <t>748313</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39762</t>
+          <t>40960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>46226</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40591</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77902</t>
+          <t>76346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25601</t>
+          <t>28461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>475341</t>
+          <t>469817</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>538274</t>
+          <t>534740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>564733</t>
+          <t>565147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>701099</t>
+          <t>695847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1057429</t>
+          <t>1055906</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1219678</t>
+          <t>1217609</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225196</t>
+          <t>229073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>280828</t>
+          <t>283859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>223251</t>
+          <t>228153</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311472</t>
+          <t>311752</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>473686</t>
+          <t>472440</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>577796</t>
+          <t>574494</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74561</t>
+          <t>75947</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112494</t>
+          <t>113185</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77553</t>
+          <t>75743</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>116460</t>
+          <t>117255</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,47 +13981,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>190458</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>161293</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>215470</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>10,69%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>190458</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>166036</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>218269</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46409</t>
+          <t>46880</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79226</t>
+          <t>76223</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55310</t>
+          <t>55275</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85612</t>
+          <t>86622</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110653</t>
+          <t>111515</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>151594</t>
+          <t>151104</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21344</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>51228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>36164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>70266</t>
+          <t>68074</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1836733</t>
+          <t>1847985</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2294534</t>
+          <t>2316231</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1472956</t>
+          <t>1488101</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1933793</t>
+          <t>1934043</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3447340</t>
+          <t>3453740</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4083860</t>
+          <t>4103383</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>789741</t>
+          <t>773833</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1103682</t>
+          <t>1095609</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>896364</t>
+          <t>911810</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1187167</t>
+          <t>1188449</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1829948</t>
+          <t>1830807</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2245558</t>
+          <t>2247191</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>221021</t>
+          <t>220428</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>325802</t>
+          <t>325393</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>312945</t>
+          <t>313480</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1056830</t>
+          <t>1021165</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>586869</t>
+          <t>588198</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1432642</t>
+          <t>1536056</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>120239</t>
+          <t>120100</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>185099</t>
+          <t>181315</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>160969</t>
+          <t>160129</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>222745</t>
+          <t>224413</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>303123</t>
+          <t>300647</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>394276</t>
+          <t>394534</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33015</t>
+          <t>32862</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>63546</t>
+          <t>63661</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>51112</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>89759</t>
+          <t>91244</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94037</t>
+          <t>93256</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>140829</t>
+          <t>140765</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">

--- a/data/trans_orig/P5701-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5701-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>236447</t>
+          <t>235820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>287924</t>
+          <t>284276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>217255</t>
+          <t>219864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>270996</t>
+          <t>271332</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>470456</t>
+          <t>474611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>541439</t>
+          <t>540705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195543</t>
+          <t>195169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242606</t>
+          <t>242497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>196198</t>
+          <t>194787</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245866</t>
+          <t>245735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>402656</t>
+          <t>405964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>471928</t>
+          <t>470165</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>159925</t>
+          <t>158767</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207235</t>
+          <t>203803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>142959</t>
+          <t>140517</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186367</t>
+          <t>186609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>312807</t>
+          <t>314807</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>376505</t>
+          <t>375395</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42594</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40570</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69222</t>
+          <t>70602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67403</t>
+          <t>67831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105304</t>
+          <t>103397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>411365</t>
+          <t>412236</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>473366</t>
+          <t>479079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>363268</t>
+          <t>359757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>422752</t>
+          <t>423061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>791864</t>
+          <t>785332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>882417</t>
+          <t>879245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>242871</t>
+          <t>241461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299457</t>
+          <t>299763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>264896</t>
+          <t>266826</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326076</t>
+          <t>324975</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>529408</t>
+          <t>523660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>607783</t>
+          <t>607963</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166588</t>
+          <t>166956</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>219153</t>
+          <t>220900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>176222</t>
+          <t>175227</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>229091</t>
+          <t>228768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>358612</t>
+          <t>354052</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>430065</t>
+          <t>430496</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28851</t>
+          <t>29074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52760</t>
+          <t>54875</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51900</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85930</t>
+          <t>82507</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87346</t>
+          <t>85528</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128726</t>
+          <t>127028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29490</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>23461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44388</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>329813</t>
+          <t>331139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382092</t>
+          <t>382365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290885</t>
+          <t>290727</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340858</t>
+          <t>342388</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>636916</t>
+          <t>634032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>706768</t>
+          <t>704834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148094</t>
+          <t>148207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193482</t>
+          <t>192293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163744</t>
+          <t>161678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208702</t>
+          <t>205029</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323203</t>
+          <t>320127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387456</t>
+          <t>383114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85524</t>
+          <t>85081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>122363</t>
+          <t>122541</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93109</t>
+          <t>91388</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131824</t>
+          <t>131561</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>188156</t>
+          <t>187647</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>241769</t>
+          <t>240735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23633</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50886</t>
+          <t>50120</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45210</t>
+          <t>44803</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73924</t>
+          <t>72815</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77325</t>
+          <t>74739</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113757</t>
+          <t>114760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20615</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46356</t>
+          <t>46359</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>384053</t>
+          <t>383136</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>444214</t>
+          <t>443288</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>426213</t>
+          <t>425539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>490371</t>
+          <t>492631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>827969</t>
+          <t>829198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>920447</t>
+          <t>915587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>227847</t>
+          <t>226173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>279590</t>
+          <t>279540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240889</t>
+          <t>239084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>293756</t>
+          <t>296605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>483071</t>
+          <t>480069</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>560315</t>
+          <t>558850</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>161323</t>
+          <t>162605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>211710</t>
+          <t>208701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>151703</t>
+          <t>152775</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>200688</t>
+          <t>200005</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>328521</t>
+          <t>329636</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>394926</t>
+          <t>399659</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57513</t>
+          <t>56821</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>94382</t>
+          <t>90287</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90721</t>
+          <t>90693</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131369</t>
+          <t>132754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158566</t>
+          <t>157200</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>209875</t>
+          <t>209973</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29550</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17312</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38926</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61273</t>
+          <t>61779</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1417007</t>
+          <t>1417219</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1529384</t>
+          <t>1534599</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1360209</t>
+          <t>1353109</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1469151</t>
+          <t>1465672</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2806532</t>
+          <t>2807715</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2964400</t>
+          <t>2969898</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>863741</t>
+          <t>861563</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>966032</t>
+          <t>964107</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>916465</t>
+          <t>913745</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1018528</t>
+          <t>1013524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1803166</t>
+          <t>1797277</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1951025</t>
+          <t>1949224</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>618861</t>
+          <t>617061</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>707187</t>
+          <t>712513</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>605616</t>
+          <t>609001</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>694996</t>
+          <t>695785</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1246598</t>
+          <t>1253632</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1378754</t>
+          <t>1383604</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>153540</t>
+          <t>153083</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>207773</t>
+          <t>207041</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>258619</t>
+          <t>256415</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>323875</t>
+          <t>322552</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>423859</t>
+          <t>425397</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>507131</t>
+          <t>508141</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>69529</t>
+          <t>70072</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>48309</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>82365</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>92518</t>
+          <t>94852</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>140720</t>
+          <t>139936</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>396023</t>
+          <t>395701</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>450324</t>
+          <t>447372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>362034</t>
+          <t>360975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>415624</t>
+          <t>412948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>772711</t>
+          <t>771325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>847324</t>
+          <t>848539</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135036</t>
+          <t>134120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178030</t>
+          <t>180033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149133</t>
+          <t>148657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196596</t>
+          <t>194172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>292655</t>
+          <t>291491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>361898</t>
+          <t>356551</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77829</t>
+          <t>77763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115525</t>
+          <t>118285</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63133</t>
+          <t>63345</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>97088</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>147378</t>
+          <t>151204</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>198700</t>
+          <t>202797</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>13667</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33520</t>
+          <t>33398</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>38201</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67750</t>
+          <t>67811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58210</t>
+          <t>58789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93365</t>
+          <t>94198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>16005</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>25740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>539875</t>
+          <t>539960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>604143</t>
+          <t>603418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>527695</t>
+          <t>524037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>593483</t>
+          <t>593360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1086092</t>
+          <t>1080995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1177173</t>
+          <t>1174270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>212984</t>
+          <t>211596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>265715</t>
+          <t>266566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245597</t>
+          <t>244980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305409</t>
+          <t>307639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>473288</t>
+          <t>472126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>555596</t>
+          <t>551973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>121029</t>
+          <t>121163</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>165691</t>
+          <t>167916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118488</t>
+          <t>118036</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162179</t>
+          <t>163395</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252704</t>
+          <t>252164</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>316381</t>
+          <t>316481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>40015</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77053</t>
+          <t>74544</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,47 +5411,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>42974</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>31352</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>58888</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>4,16%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>42974</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>31726</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>56724</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79701</t>
+          <t>80750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123089</t>
+          <t>123515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>26454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>384025</t>
+          <t>381636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>442855</t>
+          <t>439130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>379797</t>
+          <t>380948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>436142</t>
+          <t>438310</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>780874</t>
+          <t>781500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>863231</t>
+          <t>861569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148887</t>
+          <t>149420</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197934</t>
+          <t>197110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157501</t>
+          <t>158984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207421</t>
+          <t>208086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325435</t>
+          <t>321089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392220</t>
+          <t>393356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90366</t>
+          <t>92278</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130650</t>
+          <t>135289</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92128</t>
+          <t>93705</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132102</t>
+          <t>134841</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>193279</t>
+          <t>194279</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>252512</t>
+          <t>253119</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62603</t>
+          <t>63877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46955</t>
+          <t>45559</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78291</t>
+          <t>77468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86679</t>
+          <t>88259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130240</t>
+          <t>129597</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22224</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39584</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>452426</t>
+          <t>450336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>514000</t>
+          <t>514652</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>483125</t>
+          <t>480346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>548217</t>
+          <t>548828</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>947200</t>
+          <t>942241</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1039220</t>
+          <t>1041834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232073</t>
+          <t>234831</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>289923</t>
+          <t>291189</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>271801</t>
+          <t>270766</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>329987</t>
+          <t>330111</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>522325</t>
+          <t>523473</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>605471</t>
+          <t>607045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>127061</t>
+          <t>127085</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>175528</t>
+          <t>173762</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125472</t>
+          <t>124696</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>167862</t>
+          <t>170775</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>261794</t>
+          <t>261735</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>327015</t>
+          <t>327956</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32511</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57892</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58427</t>
+          <t>57413</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93447</t>
+          <t>95623</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99032</t>
+          <t>99757</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143784</t>
+          <t>141748</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19786</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24846</t>
+          <t>24294</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37599</t>
+          <t>39228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1827244</t>
+          <t>1822537</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1945721</t>
+          <t>1941520</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1808176</t>
+          <t>1805091</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1933041</t>
+          <t>1924384</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3668352</t>
+          <t>3664835</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3836888</t>
+          <t>3842713</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>775622</t>
+          <t>777706</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>875762</t>
+          <t>883528</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>878893</t>
+          <t>877023</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>988170</t>
+          <t>981908</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1675369</t>
+          <t>1678946</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1827362</t>
+          <t>1830397</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>454854</t>
+          <t>455596</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>542023</t>
+          <t>540231</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>439595</t>
+          <t>439615</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>518142</t>
+          <t>521945</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>912929</t>
+          <t>914324</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1035570</t>
+          <t>1034948</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>142875</t>
+          <t>140615</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>197493</t>
+          <t>198348</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>203350</t>
+          <t>204236</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>265118</t>
+          <t>265139</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>358975</t>
+          <t>362606</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>444082</t>
+          <t>444279</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26345</t>
+          <t>27610</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54108</t>
+          <t>52602</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37843</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>68331</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70809</t>
+          <t>69847</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>111622</t>
+          <t>108563</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>275847</t>
+          <t>274915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>327812</t>
+          <t>328981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>243728</t>
+          <t>242410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>298323</t>
+          <t>294669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531935</t>
+          <t>532860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>602365</t>
+          <t>608087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215314</t>
+          <t>213421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263690</t>
+          <t>263127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231905</t>
+          <t>234529</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284811</t>
+          <t>286920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>463787</t>
+          <t>465496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531045</t>
+          <t>534158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82487</t>
+          <t>83054</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120262</t>
+          <t>120652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81774</t>
+          <t>83773</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119306</t>
+          <t>119854</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>176735</t>
+          <t>174621</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>229257</t>
+          <t>226569</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>19111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25807</t>
+          <t>24916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>50159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>82421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>14550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>418646</t>
+          <t>413377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>484980</t>
+          <t>478782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>372874</t>
+          <t>370260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>432631</t>
+          <t>432928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>805803</t>
+          <t>806710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>897425</t>
+          <t>895388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>358364</t>
+          <t>357388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421294</t>
+          <t>419033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408863</t>
+          <t>407922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>470528</t>
+          <t>472011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>781540</t>
+          <t>780286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>872355</t>
+          <t>871210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111812</t>
+          <t>110635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>155153</t>
+          <t>154218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117080</t>
+          <t>117356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163476</t>
+          <t>163217</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>242420</t>
+          <t>239089</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>307336</t>
+          <t>303743</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36807</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64108</t>
+          <t>64218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>36831</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68805</t>
+          <t>68208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79515</t>
+          <t>81948</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119955</t>
+          <t>124063</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>22874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284291</t>
+          <t>284207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>340426</t>
+          <t>339940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289184</t>
+          <t>290279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>344760</t>
+          <t>344745</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>592968</t>
+          <t>591397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>670755</t>
+          <t>666751</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>251556</t>
+          <t>252446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>308173</t>
+          <t>307106</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>257766</t>
+          <t>257545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>311769</t>
+          <t>311357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>524147</t>
+          <t>526469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>603737</t>
+          <t>602557</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104683</t>
+          <t>105588</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148399</t>
+          <t>147072</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>122165</t>
+          <t>122250</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>168531</t>
+          <t>167040</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>241033</t>
+          <t>240100</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>299693</t>
+          <t>299310</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22784</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46713</t>
+          <t>45521</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>46489</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52487</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86082</t>
+          <t>83289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>20965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>359331</t>
+          <t>360333</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>420403</t>
+          <t>424033</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>413621</t>
+          <t>412121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>474290</t>
+          <t>475228</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>788915</t>
+          <t>793118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>877348</t>
+          <t>878111</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>311681</t>
+          <t>311801</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>371217</t>
+          <t>370530</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>350885</t>
+          <t>349628</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>413273</t>
+          <t>414998</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>681057</t>
+          <t>676019</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>765926</t>
+          <t>765650</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>130264</t>
+          <t>130917</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>176059</t>
+          <t>174628</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125609</t>
+          <t>127336</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>171571</t>
+          <t>176713</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>269003</t>
+          <t>268685</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>336526</t>
+          <t>333368</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29664</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55083</t>
+          <t>55732</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47021</t>
+          <t>46919</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78939</t>
+          <t>78710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84661</t>
+          <t>83149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127453</t>
+          <t>124350</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>32244</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1390324</t>
+          <t>1400061</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1509621</t>
+          <t>1509145</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1375855</t>
+          <t>1373484</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1492138</t>
+          <t>1489563</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2800998</t>
+          <t>2807211</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2969043</t>
+          <t>2973471</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1192874</t>
+          <t>1196325</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1306138</t>
+          <t>1302886</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1308061</t>
+          <t>1305690</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1424247</t>
+          <t>1425445</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2528869</t>
+          <t>2530325</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2695303</t>
+          <t>2691017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>473096</t>
+          <t>471777</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>557011</t>
+          <t>555664</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>489368</t>
+          <t>487420</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>576524</t>
+          <t>572577</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>982970</t>
+          <t>983597</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1101053</t>
+          <t>1102015</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>127900</t>
+          <t>126745</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>178899</t>
+          <t>177181</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156679</t>
+          <t>154756</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>210596</t>
+          <t>210111</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>295481</t>
+          <t>296629</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>368828</t>
+          <t>371556</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>39439</t>
+          <t>38321</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19849</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42929</t>
+          <t>43984</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43161</t>
+          <t>43527</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>75032</t>
+          <t>75681</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>344880</t>
+          <t>368374</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313626</t>
+          <t>339267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>372272</t>
+          <t>395876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>351060</t>
+          <t>376101</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>331650</t>
+          <t>354251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>373049</t>
+          <t>396742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>695940</t>
+          <t>744474</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>659994</t>
+          <t>711012</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>732158</t>
+          <t>779214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>54,82%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>187299</t>
+          <t>202031</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>164466</t>
+          <t>179204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214766</t>
+          <t>228028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>223151</t>
+          <t>243543</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203745</t>
+          <t>221371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241939</t>
+          <t>262317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>410451</t>
+          <t>445574</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>379572</t>
+          <t>417118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441987</t>
+          <t>478986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>66953</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47274</t>
+          <t>52995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75511</t>
+          <t>84767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,22 +11915,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54455</t>
+          <t>58677</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45077</t>
+          <t>48898</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65708</t>
+          <t>70320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>114912</t>
+          <t>125630</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97179</t>
+          <t>108562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>134183</t>
+          <t>144938</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30678</t>
+          <t>36689</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21402</t>
+          <t>26499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>43382</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>33980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46971</t>
+          <t>54894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67596</t>
+          <t>80071</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55783</t>
+          <t>65299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83448</t>
+          <t>96241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22475</t>
+          <t>31020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13592</t>
+          <t>17479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>40737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634642</t>
+          <t>689896</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>634642</t>
+          <t>689896</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634642</t>
+          <t>689896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>674339</t>
+          <t>731496</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>674339</t>
+          <t>731496</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>674339</t>
+          <t>731496</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1308981</t>
+          <t>1421391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1308981</t>
+          <t>1421391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1308981</t>
+          <t>1421391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>746261</t>
+          <t>549809</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>614319</t>
+          <t>512803</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>988986</t>
+          <t>586981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>458830</t>
+          <t>498226</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>432538</t>
+          <t>469910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>485270</t>
+          <t>527076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1205091</t>
+          <t>1048035</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1068797</t>
+          <t>1004677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1525432</t>
+          <t>1100655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>323422</t>
+          <t>357012</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158625</t>
+          <t>323101</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422093</t>
+          <t>389933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>343748</t>
+          <t>390697</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318456</t>
+          <t>361827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>366740</t>
+          <t>416119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>667170</t>
+          <t>747710</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>443685</t>
+          <t>701802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>767211</t>
+          <t>788150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74116</t>
+          <t>79143</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37142</t>
+          <t>62878</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109719</t>
+          <t>98373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80580</t>
+          <t>93340</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68827</t>
+          <t>79422</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96859</t>
+          <t>109829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>154696</t>
+          <t>172483</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99456</t>
+          <t>148239</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>186173</t>
+          <t>195600</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>48020</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>36609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>66192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57097</t>
+          <t>69063</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46429</t>
+          <t>56818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71123</t>
+          <t>88263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62627</t>
+          <t>97518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116870</t>
+          <t>139709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>21971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17393</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>29633</t>
+          <t>32095</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>22598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43720</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047048</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047048</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>957648</t>
+          <t>1070357</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>957648</t>
+          <t>1070357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>957648</t>
+          <t>1070357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2150350</t>
+          <t>2117405</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2150350</t>
+          <t>2117405</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2150350</t>
+          <t>2117405</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>375538</t>
+          <t>417431</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>346090</t>
+          <t>384271</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>408978</t>
+          <t>451651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>365704</t>
+          <t>385754</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186449</t>
+          <t>360399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>486881</t>
+          <t>412275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>741242</t>
+          <t>803185</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>495012</t>
+          <t>762706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>868614</t>
+          <t>848910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>239057</t>
+          <t>266375</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210290</t>
+          <t>233048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>269931</t>
+          <t>297806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>246909</t>
+          <t>283240</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121907</t>
+          <t>259509</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>328627</t>
+          <t>307938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>485966</t>
+          <t>549615</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332489</t>
+          <t>505924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>571339</t>
+          <t>583590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55097</t>
+          <t>70544</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>53598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76935</t>
+          <t>94484</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>278233</t>
+          <t>86415</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86734</t>
+          <t>71086</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>595548</t>
+          <t>105412</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>333329</t>
+          <t>156958</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>137149</t>
+          <t>134827</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>748313</t>
+          <t>187732</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28873</t>
+          <t>40602</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40960</t>
+          <t>54712</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32341</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46226</t>
+          <t>55018</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>61215</t>
+          <t>82995</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39597</t>
+          <t>66689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76346</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12845</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>22579</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28461</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>505086</t>
+          <t>521385</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>469817</t>
+          <t>487613</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>534740</t>
+          <t>551786</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>607299</t>
+          <t>573420</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>565147</t>
+          <t>542510</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>695847</t>
+          <t>600683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1112385</t>
+          <t>1094804</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1055906</t>
+          <t>1046124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1217609</t>
+          <t>1140520</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>253213</t>
+          <t>277063</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229073</t>
+          <t>248975</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>283859</t>
+          <t>306220</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>281179</t>
+          <t>312283</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>228153</t>
+          <t>286343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311752</t>
+          <t>339801</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>534391</t>
+          <t>589345</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>472440</t>
+          <t>552971</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>574494</t>
+          <t>631704</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -13926,27 +13926,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>92011</t>
+          <t>99952</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75947</t>
+          <t>81246</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113185</t>
+          <t>120917</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>98447</t>
+          <t>107991</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75743</t>
+          <t>91521</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>117255</t>
+          <t>126215</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>190458</t>
+          <t>207942</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>161293</t>
+          <t>181357</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>215470</t>
+          <t>234434</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -14039,67 +14039,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>59969</t>
+          <t>70321</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46880</t>
+          <t>56433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>76223</t>
+          <t>89390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>85441</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>72040</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>101543</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>6,47%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>70936</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>55275</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>86622</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>130905</t>
+          <t>155762</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111515</t>
+          <t>133770</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>151104</t>
+          <t>180401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>21342</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25146</t>
+          <t>30919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>35179</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>26040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51228</t>
+          <t>47928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>47708</t>
+          <t>56522</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36164</t>
+          <t>43687</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68074</t>
+          <t>71644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1089017</t>
+          <t>1114313</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1089017</t>
+          <t>1114313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1089017</t>
+          <t>1114313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2015848</t>
+          <t>2104375</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2015848</t>
+          <t>2104375</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2015848</t>
+          <t>2104375</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1971765</t>
+          <t>1856999</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1847985</t>
+          <t>1792030</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2316231</t>
+          <t>1926513</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1782893</t>
+          <t>1833500</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1488101</t>
+          <t>1779715</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1934043</t>
+          <t>1886987</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3754658</t>
+          <t>3690499</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3453740</t>
+          <t>3603666</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4103383</t>
+          <t>3774814</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1002991</t>
+          <t>1102481</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>773833</t>
+          <t>1046655</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1095609</t>
+          <t>1159972</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1094987</t>
+          <t>1229762</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>911810</t>
+          <t>1180645</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1188449</t>
+          <t>1279529</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2097978</t>
+          <t>2332243</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1830807</t>
+          <t>2258630</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2247191</t>
+          <t>2409106</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>281682</t>
+          <t>316592</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>220428</t>
+          <t>284133</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>325393</t>
+          <t>357670</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>511714</t>
+          <t>346422</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>313480</t>
+          <t>317942</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1021165</t>
+          <t>379173</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>793396</t>
+          <t>663014</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>588198</t>
+          <t>615031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1536056</t>
+          <t>713007</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>156185</t>
+          <t>195633</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>120100</t>
+          <t>169728</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>181315</t>
+          <t>225525</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>197292</t>
+          <t>240278</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>160129</t>
+          <t>216207</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>224413</t>
+          <t>267540</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>353477</t>
+          <t>435911</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>300647</t>
+          <t>401892</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>394534</t>
+          <t>473490</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>46233</t>
+          <t>58375</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32862</t>
+          <t>43993</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>63661</t>
+          <t>78167</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>67484</t>
+          <t>78462</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>91244</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>113717</t>
+          <t>136837</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93256</t>
+          <t>115780</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>140765</t>
+          <t>162801</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3458855</t>
+          <t>3530079</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3458855</t>
+          <t>3530079</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3458855</t>
+          <t>3530079</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3654371</t>
+          <t>3728424</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3654371</t>
+          <t>3728424</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3654371</t>
+          <t>3728424</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7113226</t>
+          <t>7258504</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7113226</t>
+          <t>7258504</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7113226</t>
+          <t>7258504</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
